--- a/data_extactor/batch_10_fa/trimmed/batch_0072_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0072_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
+          <t>نظارت | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | راهبردهای یادگیری | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | طراحی | مکانیک | ریاضیات</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | طراحی | مکانیک | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | تجسم فضایی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | تجسم</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران ساخت و ساز | مهندسان برق | برق‌کاران | سرپرستان رده‌اول مشاغل ساختمانی و استخراج | کارشناسان مدیریت پروژه | مهندسان سامانه‌های انرژی خورشیدی | نصابان سامانه‌های فتوولتائیک خورشیدی</t>
+          <t>مدیران پروژه‌های ساختمانی | مهندسان برق | برق‌کاران | سرپرستان رده‌اول مشاغل ساختمانی، عمرانی و استخراج | کارشناسان مدیریت پروژه | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | قدرت عضلانی تنه | قدرت ایستا</t>
+          <t>دقت کنترل | بینایی نزدیک | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | قدرت تنه | قدرت ایستا</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مکانیک‌های ماشین‌آلات صنعتی | نصابان و ترازکاران ماشین‌آلات سنگین (میلرایت‌ها) | لوله‌کشان، لوله‌کشان صنعتی و اتصالات بخار | ورق‌کاران و نصابان قطعات فلزی | مهندسان تأسیسات ثابت و اپراتورهای دیگ بخار | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
+          <t>مکانیک‌های ماشین‌آلات صنعتی | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | کارگران ورق‌کاری فلزی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | سازندگان و مونتاژکاران سازه‌های فلزی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | ایمنی و امنیت عمومی | تولید و فرآوری | طراحی | مکانیک</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>قدرت عضلانی تنه | دید نزدیک | ثبات دست و بازو | چابکی دستی | قدرت ایستا | تجسم فضایی | هماهنگی اندام‌ها</t>
+          <t>قدرت تنه | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | قدرت ایستا | تجسم | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>نجاران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | سفیدکاران و گچ‌کاران سنتی و پلیمری | کارگران آرماتوربندی و تقویت اسکلت | سنگ‌کاران ساختمانی</t>
+          <t>نجاران و درودگران | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | سفیدکاران و گچ‌کاران نما | آرماتوربندان و نصابان میلگرد | سنگ‌کاران ساختمانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نظارت | ریاضیات | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نظارت | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ساخت و ساز | طراحی | ریاضیات | مکانیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زبان انگلیسی</t>
+          <t>ساختمان و ساخت‌وساز | طراحی | ریاضیات | مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>قدرت ایستا | قدرت عضلانی تنه | دید نزدیک | ثبات دست و بازو | چابکی دستی | تجسم فضایی | استقامت بدنی</t>
+          <t>قدرت ایستا | قدرت تنه | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | تجسم | استقامت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | سنگ‌فرش‌کاران و بلوک‌فرش‌کاران راه‌ها | سنگ‌تراشان و حجّاران صنعتی | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>بنایان و سفت‌کاران ساختمان | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | سنگ‌فرش‌کاران و موزاییک‌ریزان قطعه‌ای | سنگ‌تراشان و حکاکان صنعتی سنگ | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات</t>
+          <t>گوش دادن فعال | تفکر انتقادی | نظارت | درک مطلب | سخن گفتن | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | طراحی | مهندسی و فناوری | ایمنی و امنیت عمومی | مکانیک</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | تجسم فضایی | دید نزدیک | چابکی دستی | چابکی انگشتان | قدرت عضلانی تنه | ثبات دست و بازو</t>
+          <t>حساسیت به مسئله | تجسم | بینایی نزدیک | مهارت دستی | مهارت انگشتان | قدرت تنه | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساده ساختمانی | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کمک‌نجاران | کارگران سازه‌های اسکلت فلزی و فولادی</t>
+          <t>بنایان و سفت‌کاران ساختمان | کابینت‌سازان و نجاران کارگاهی | بتن‌ریزان و پرداخت‌کاران بتن | کارگران ساختمانی | نصابان دیوار کاذب و تایل سقف | کمک‌نجاران | اسکلت‌سازان و نصابان سازه‌های فولادی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | ریاضیات | مدیریت و امور اداری | زبان انگلیسی | ساخت و ساز | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | ریاضیات | مدیریت و اداره | زبان انگلیسی | ساختمان و ساخت‌وساز | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>وسعت دامنه حرکتی | قدرت عضلانی تنه | دید نزدیک | قدرت ایستا | ثبات دست و بازو | چابکی دستی | استقامت بدنی</t>
+          <t>انعطاف‌پذیری دامنه حرکت | قدرت تنه | بینایی نزدیک | قدرت ایستا | ثبات دست و بازو | مهارت دستی | استقامت</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>نجاران | نصابان صفحات گچی (کناف) و تایل‌های سقفی | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | عایق‌کاران کف، سقف و دیوار | نصابان کاغذ دیواری | رویه‌کوبان مبل و روکش‌کاران</t>
+          <t>نجاران و درودگران | نصابان دیوار کاذب و تایل سقف | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | ساب‌زنان و پرداخت‌کاران کف | عایق‌کاران کف، سقف و دیوار | نصابان کاغذ دیواری | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن</t>
+          <t>گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | ریاضیات | مکانیک | تولید و فرآوری | طراحی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | وسعت دامنه حرکتی | ثبات دست و بازو | قدرت ایستا | چابکی انگشتان | چابکی دستی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | ثبات دست و بازو | قدرت ایستا | مهارت انگشتان | مهارت دستی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>نجاران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان صفحات گچی (کناف) و تایل‌های سقفی | ساب‌زنان و پرداخت‌کاران کف | نصابان کاغذ دیواری | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | نصابان دیوار کاذب و تایل سقف | ساب‌زنان و پرداخت‌کاران کف | نصابان کاغذ دیواری | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FloorCOST Estimator for Excel | Flooring Technologies QFloors | Measure Square | Pacific Solutions FloorRight | Microsoft Excel | نرم‌افزار نقشه‌کشی و پلان کف | Vimeo</t>
+          <t>نرم‌افزار برنامه‌ریزی چیدمان طبقات | Flooring Technologies QFloors | Measure Square | Pacific Solutions FloorRight | Microsoft Excel | نرم‌افزار نقشه‌کشی و پلان کف | Vimeo</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال</t>
+          <t>گوش دادن فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ساخت و ساز | خدمات مشتریان و خدمات فردی | زبان انگلیسی | تولید و فرآوری | مدیریت و امور اداری | مکانیک</t>
+          <t>ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | قدرت عضلانی تنه | چابکی انگشتان | استقامت بدنی</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | قدرت تنه | مهارت انگشتان | استقامت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نجاران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | رنگ‌کاران و پرداخت‌کاران چوب و مبلمان | نقاشان ساختمان و کارهای تعمیراتی | کاشی‌کاران و سنگ‌کاران ظریف</t>
+          <t>نجاران و درودگران | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | نقاشان ساختمان و تاسیسات | کاشی‌کاران و سنگ‌کاران ظریف</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | ریاضیات | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | ریاضیات | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ساخت و ساز | ریاضیات | خدمات مشتریان و خدمات فردی | طراحی</t>
+          <t>ساختمان و ساخت‌وساز | ریاضیات | خدمات مشتری و شخصی | طراحی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | وسعت دامنه حرکتی | قدرت عضلانی تنه | قدرت ایستا | چابکی انگشتان | چابکی دستی</t>
+          <t>تجسم | بینایی نزدیک | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت ایستا | مهارت انگشتان | مهارت دستی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | سفیدکاران و گچ‌کاران سنتی و پلیمری | سنگ‌کاران ساختمانی</t>
+          <t>بنایان و سفت‌کاران ساختمان | موکت‌کاران و نصابان فرش | بتن‌ریزان و پرداخت‌کاران بتن | کف‌پوش‌کاران به‌جز فرش، چوب و کاشی سخت | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | سفیدکاران و گچ‌کاران نما | سنگ‌کاران ساختمانی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | ساخت و ساز | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>زبان انگلیسی | ساختمان و ساخت‌وساز | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | قدرت عضلانی تنه | هماهنگی اندام‌ها | دید نزدیک | ثبات دست و بازو | قدرت دینامیک | استقامت بدنی</t>
+          <t>مهارت دستی | قدرت تنه | هماهنگی چند عضو | بینایی نزدیک | ثبات دست و بازو | قدرت پویا | استقامت</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>بنایان و سفت‌کاران ساختمان | نجاران | کارگران ساده ساختمانی | کمک‌بنایان آجر، بلوک، سنگ و کاشی و سرامیک | اپراتورهای ماشین‌آلات روسازی، آسفالت و تراکم بتن | کارگران آرماتوربندی و تقویت اسکلت | موزاییک‌سازان، واش‌بتن‌کاران و نصابان بتن درجا</t>
+          <t>بنایان و سفت‌کاران ساختمان | نجاران و درودگران | کارگران ساختمانی | کمک‌بناها، کمک‌بلوک‌چین‌ها، کمک‌سنگ‌تراشان و کمک‌نصابان کاشی و مرمر | اپراتورهای تجهیزات آسفالت‌ریزی، پخش و کوبش | آرماتوربندان و نصابان میلگرد | موزاییک‌کاران و پرداخت‌کاران موزاییک درجا</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
